--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2019_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2019_arica_y_parinacota.xlsx
@@ -126,7 +126,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 13:56</t>
+    <t xml:space="preserve">2026-09-24 00:47</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -773,7 +773,7 @@
         <v>-0.79</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="19">
@@ -787,7 +787,7 @@
         <v>-0.27</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="20">
@@ -801,7 +801,7 @@
         <v>-0.66</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="21">
@@ -812,10 +812,10 @@
         <v>23</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>-0.39</v>
+        <v>-0.4</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="22">

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2019_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2019_arica_y_parinacota.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -126,7 +126,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:47</t>
+    <t xml:space="preserve">2026-10-01 23:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2019_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2019_arica_y_parinacota.xlsx
@@ -126,7 +126,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:07</t>
+    <t xml:space="preserve">2026-10-05 19:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
